--- a/thaco/color/1_MID_Office_Viet.xlsx
+++ b/thaco/color/1_MID_Office_Viet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adity/Documents/GitHub/gitlocal/thaco/color/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAD65618-6450-1E46-BDA6-886750DACB2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0017099A-18E6-2643-B7D6-A8419B367203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="35720" windowHeight="18900" tabRatio="761" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="35720" windowHeight="18900" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bảng lương CB-NV" sheetId="1" r:id="rId1"/>
@@ -4545,7 +4545,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="237">
   <si>
     <t>COMPANY …..............</t>
   </si>
@@ -5270,6 +5270,9 @@
   </si>
   <si>
     <t>Các khoản trừ</t>
+  </si>
+  <si>
+    <t>H</t>
   </si>
 </sst>
 </file>
@@ -6075,7 +6078,7 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="25" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="516">
+  <cellXfs count="517">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -7206,9 +7209,6 @@
     <xf numFmtId="164" fontId="4" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="64" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7439,6 +7439,12 @@
     </xf>
     <xf numFmtId="164" fontId="15" fillId="6" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="64" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="9">
@@ -8690,7 +8696,7 @@
       <c r="CC7" s="235"/>
       <c r="CD7" s="235"/>
       <c r="CE7" s="210" t="s">
-        <v>155</v>
+        <v>236</v>
       </c>
     </row>
     <row r="8" spans="1:87" s="213" customFormat="1" ht="19.25" customHeight="1">
@@ -15437,90 +15443,88 @@
       <c r="CB2" s="268"/>
     </row>
     <row r="3" spans="1:85" s="240" customFormat="1" ht="24" customHeight="1" outlineLevel="1">
-      <c r="A3" s="440"/>
-      <c r="B3" s="439"/>
-      <c r="C3" s="439"/>
-      <c r="D3" s="439"/>
-      <c r="E3" s="439"/>
-      <c r="F3" s="439"/>
-      <c r="G3" s="439"/>
-      <c r="H3" s="439"/>
-      <c r="I3" s="439"/>
-      <c r="J3" s="439"/>
-      <c r="K3" s="439"/>
-      <c r="L3" s="439"/>
-      <c r="M3" s="439"/>
-      <c r="N3" s="439"/>
-      <c r="O3" s="439"/>
-      <c r="P3" s="439"/>
-      <c r="Q3" s="439"/>
-      <c r="R3" s="439"/>
-      <c r="S3" s="439"/>
-      <c r="T3" s="439"/>
-      <c r="U3" s="439"/>
-      <c r="V3" s="439"/>
-      <c r="W3" s="439"/>
-      <c r="X3" s="439"/>
-      <c r="Y3" s="439"/>
-      <c r="Z3" s="439"/>
-      <c r="AA3" s="439"/>
-      <c r="AB3" s="439"/>
-      <c r="AC3" s="439"/>
-      <c r="AD3" s="439"/>
-      <c r="AE3" s="439"/>
-      <c r="AF3" s="439"/>
-      <c r="AG3" s="439"/>
-      <c r="AH3" s="439"/>
-      <c r="AI3" s="439"/>
-      <c r="AJ3" s="439"/>
-      <c r="AK3" s="439"/>
-      <c r="AL3" s="439"/>
-      <c r="AM3" s="439"/>
-      <c r="AN3" s="439"/>
-      <c r="AO3" s="439"/>
-      <c r="AP3" s="439"/>
-      <c r="AQ3" s="439"/>
-      <c r="AR3" s="439"/>
-      <c r="AS3" s="439"/>
-      <c r="AT3" s="439"/>
-      <c r="AU3" s="439"/>
-      <c r="AV3" s="439"/>
-      <c r="AW3" s="439"/>
-      <c r="AX3" s="439"/>
-      <c r="AY3" s="439"/>
-      <c r="AZ3" s="439"/>
-      <c r="BA3" s="439"/>
-      <c r="BB3" s="439"/>
-      <c r="BC3" s="439"/>
-      <c r="BD3" s="439"/>
-      <c r="BE3" s="439"/>
-      <c r="BF3" s="439"/>
-      <c r="BG3" s="439"/>
-      <c r="BH3" s="439"/>
-      <c r="BI3" s="439"/>
-      <c r="BJ3" s="439"/>
-      <c r="BK3" s="439"/>
-      <c r="BL3" s="439"/>
-      <c r="BM3" s="439"/>
-      <c r="BN3" s="439"/>
-      <c r="BO3" s="439"/>
-      <c r="BP3" s="439"/>
-      <c r="BQ3" s="439"/>
-      <c r="BR3" s="439"/>
-      <c r="BS3" s="439"/>
-      <c r="BT3" s="439"/>
-      <c r="BU3" s="438" t="s">
-        <v>2</v>
-      </c>
-      <c r="BV3" s="439"/>
-      <c r="BW3" s="439"/>
-      <c r="BX3" s="439"/>
-      <c r="BY3" s="439"/>
-      <c r="BZ3" s="439"/>
+      <c r="A3" s="439"/>
+      <c r="B3" s="438"/>
+      <c r="C3" s="438"/>
+      <c r="D3" s="438"/>
+      <c r="E3" s="438"/>
+      <c r="F3" s="438"/>
+      <c r="G3" s="438"/>
+      <c r="H3" s="438"/>
+      <c r="I3" s="438"/>
+      <c r="J3" s="438"/>
+      <c r="K3" s="438"/>
+      <c r="L3" s="438"/>
+      <c r="M3" s="438"/>
+      <c r="N3" s="438"/>
+      <c r="O3" s="438"/>
+      <c r="P3" s="438"/>
+      <c r="Q3" s="438"/>
+      <c r="R3" s="438"/>
+      <c r="S3" s="438"/>
+      <c r="T3" s="438"/>
+      <c r="U3" s="438"/>
+      <c r="V3" s="438"/>
+      <c r="W3" s="438"/>
+      <c r="X3" s="438"/>
+      <c r="Y3" s="438"/>
+      <c r="Z3" s="438"/>
+      <c r="AA3" s="438"/>
+      <c r="AB3" s="438"/>
+      <c r="AC3" s="438"/>
+      <c r="AD3" s="438"/>
+      <c r="AE3" s="438"/>
+      <c r="AF3" s="438"/>
+      <c r="AG3" s="438"/>
+      <c r="AH3" s="438"/>
+      <c r="AI3" s="438"/>
+      <c r="AJ3" s="438"/>
+      <c r="AK3" s="438"/>
+      <c r="AL3" s="438"/>
+      <c r="AM3" s="438"/>
+      <c r="AN3" s="438"/>
+      <c r="AO3" s="438"/>
+      <c r="AP3" s="438"/>
+      <c r="AQ3" s="438"/>
+      <c r="AR3" s="438"/>
+      <c r="AS3" s="438"/>
+      <c r="AT3" s="438"/>
+      <c r="AU3" s="438"/>
+      <c r="AV3" s="438"/>
+      <c r="AW3" s="438"/>
+      <c r="AX3" s="438"/>
+      <c r="AY3" s="438"/>
+      <c r="AZ3" s="438"/>
+      <c r="BA3" s="438"/>
+      <c r="BB3" s="438"/>
+      <c r="BC3" s="438"/>
+      <c r="BD3" s="438"/>
+      <c r="BE3" s="438"/>
+      <c r="BF3" s="438"/>
+      <c r="BG3" s="438"/>
+      <c r="BH3" s="438"/>
+      <c r="BI3" s="438"/>
+      <c r="BJ3" s="438"/>
+      <c r="BK3" s="438"/>
+      <c r="BL3" s="438"/>
+      <c r="BM3" s="438"/>
+      <c r="BN3" s="438"/>
+      <c r="BO3" s="438"/>
+      <c r="BP3" s="438"/>
+      <c r="BQ3" s="438"/>
+      <c r="BR3" s="438"/>
+      <c r="BS3" s="438"/>
+      <c r="BT3" s="438"/>
+      <c r="BU3" s="515"/>
+      <c r="BV3" s="516"/>
+      <c r="BW3" s="516"/>
+      <c r="BX3" s="516"/>
+      <c r="BY3" s="516"/>
+      <c r="BZ3" s="516"/>
       <c r="CA3" s="270"/>
       <c r="CB3" s="270"/>
     </row>
-    <row r="4" spans="1:85" s="240" customFormat="1" ht="21.5" hidden="1" customHeight="1" outlineLevel="1">
+    <row r="4" spans="1:85" s="240" customFormat="1" ht="21.5" customHeight="1" outlineLevel="1">
       <c r="A4" s="271"/>
       <c r="B4" s="271"/>
       <c r="C4" s="271"/>
@@ -15592,16 +15596,16 @@
       <c r="BR4" s="271"/>
       <c r="BS4" s="271"/>
       <c r="BT4" s="271"/>
-      <c r="BU4" s="439"/>
-      <c r="BV4" s="439"/>
-      <c r="BW4" s="439"/>
-      <c r="BX4" s="439"/>
-      <c r="BY4" s="439"/>
-      <c r="BZ4" s="439"/>
+      <c r="BU4" s="516"/>
+      <c r="BV4" s="516"/>
+      <c r="BW4" s="516"/>
+      <c r="BX4" s="516"/>
+      <c r="BY4" s="516"/>
+      <c r="BZ4" s="516"/>
       <c r="CA4" s="270"/>
       <c r="CB4" s="270"/>
     </row>
-    <row r="5" spans="1:85" s="240" customFormat="1" ht="20.25" hidden="1" customHeight="1" outlineLevel="1">
+    <row r="5" spans="1:85" s="240" customFormat="1" ht="20.25" customHeight="1" outlineLevel="1">
       <c r="A5" s="271"/>
       <c r="B5" s="271"/>
       <c r="C5" s="271"/>
@@ -15673,16 +15677,16 @@
       <c r="BR5" s="271"/>
       <c r="BS5" s="271"/>
       <c r="BT5" s="271"/>
-      <c r="BU5" s="439"/>
-      <c r="BV5" s="439"/>
-      <c r="BW5" s="439"/>
-      <c r="BX5" s="439"/>
-      <c r="BY5" s="439"/>
-      <c r="BZ5" s="439"/>
+      <c r="BU5" s="516"/>
+      <c r="BV5" s="516"/>
+      <c r="BW5" s="516"/>
+      <c r="BX5" s="516"/>
+      <c r="BY5" s="516"/>
+      <c r="BZ5" s="516"/>
       <c r="CA5" s="270"/>
       <c r="CB5" s="270"/>
     </row>
-    <row r="6" spans="1:85" s="240" customFormat="1" ht="18.75" hidden="1" customHeight="1" outlineLevel="1">
+    <row r="6" spans="1:85" s="240" customFormat="1" ht="18.75" customHeight="1" outlineLevel="1">
       <c r="A6" s="273"/>
       <c r="B6" s="273"/>
       <c r="C6" s="273"/>
@@ -15754,16 +15758,16 @@
       <c r="BR6" s="273"/>
       <c r="BS6" s="273"/>
       <c r="BT6" s="273"/>
-      <c r="BU6" s="439"/>
-      <c r="BV6" s="439"/>
-      <c r="BW6" s="439"/>
-      <c r="BX6" s="439"/>
-      <c r="BY6" s="439"/>
-      <c r="BZ6" s="439"/>
+      <c r="BU6" s="516"/>
+      <c r="BV6" s="516"/>
+      <c r="BW6" s="516"/>
+      <c r="BX6" s="516"/>
+      <c r="BY6" s="516"/>
+      <c r="BZ6" s="516"/>
       <c r="CA6" s="270"/>
       <c r="CB6" s="270"/>
     </row>
-    <row r="7" spans="1:85" s="240" customFormat="1" ht="12.75" hidden="1" customHeight="1" outlineLevel="1">
+    <row r="7" spans="1:85" s="240" customFormat="1" ht="12.75" customHeight="1" outlineLevel="1">
       <c r="A7" s="43"/>
       <c r="B7" s="281"/>
       <c r="C7" s="43"/>
@@ -15845,34 +15849,34 @@
       <c r="CB7" s="283"/>
     </row>
     <row r="8" spans="1:85" s="330" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A8" s="442" t="s">
+      <c r="A8" s="441" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="443" t="s">
+      <c r="B8" s="442" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="444" t="s">
+      <c r="C8" s="443" t="s">
         <v>162</v>
       </c>
-      <c r="D8" s="445" t="s">
+      <c r="D8" s="444" t="s">
         <v>163</v>
       </c>
-      <c r="E8" s="445" t="s">
+      <c r="E8" s="444" t="s">
         <v>164</v>
       </c>
-      <c r="F8" s="446" t="s">
+      <c r="F8" s="445" t="s">
         <v>142</v>
       </c>
-      <c r="G8" s="447" t="s">
+      <c r="G8" s="446" t="s">
         <v>165</v>
       </c>
-      <c r="H8" s="448" t="s">
+      <c r="H8" s="447" t="s">
         <v>166</v>
       </c>
-      <c r="I8" s="448" t="s">
+      <c r="I8" s="447" t="s">
         <v>167</v>
       </c>
-      <c r="J8" s="447" t="s">
+      <c r="J8" s="446" t="s">
         <v>168</v>
       </c>
       <c r="K8" s="435" t="s">
@@ -15891,91 +15895,91 @@
       <c r="V8" s="436"/>
       <c r="W8" s="436"/>
       <c r="X8" s="436"/>
-      <c r="Y8" s="513" t="s">
+      <c r="Y8" s="512" t="s">
         <v>200</v>
       </c>
-      <c r="Z8" s="514"/>
-      <c r="AA8" s="514"/>
-      <c r="AB8" s="514"/>
-      <c r="AC8" s="514"/>
-      <c r="AD8" s="514"/>
-      <c r="AE8" s="514"/>
-      <c r="AF8" s="514"/>
-      <c r="AG8" s="514"/>
-      <c r="AH8" s="514"/>
-      <c r="AI8" s="514"/>
-      <c r="AJ8" s="514"/>
-      <c r="AK8" s="514"/>
-      <c r="AL8" s="514"/>
-      <c r="AM8" s="514"/>
-      <c r="AN8" s="514"/>
-      <c r="AO8" s="515"/>
-      <c r="AP8" s="447" t="s">
+      <c r="Z8" s="513"/>
+      <c r="AA8" s="513"/>
+      <c r="AB8" s="513"/>
+      <c r="AC8" s="513"/>
+      <c r="AD8" s="513"/>
+      <c r="AE8" s="513"/>
+      <c r="AF8" s="513"/>
+      <c r="AG8" s="513"/>
+      <c r="AH8" s="513"/>
+      <c r="AI8" s="513"/>
+      <c r="AJ8" s="513"/>
+      <c r="AK8" s="513"/>
+      <c r="AL8" s="513"/>
+      <c r="AM8" s="513"/>
+      <c r="AN8" s="513"/>
+      <c r="AO8" s="514"/>
+      <c r="AP8" s="446" t="s">
         <v>201</v>
       </c>
-      <c r="AQ8" s="447" t="s">
+      <c r="AQ8" s="446" t="s">
         <v>202</v>
       </c>
-      <c r="AR8" s="447" t="s">
+      <c r="AR8" s="446" t="s">
         <v>203</v>
       </c>
-      <c r="AS8" s="447" t="s">
+      <c r="AS8" s="446" t="s">
         <v>204</v>
       </c>
-      <c r="AT8" s="447" t="s">
+      <c r="AT8" s="446" t="s">
         <v>205</v>
       </c>
-      <c r="AU8" s="447" t="s">
+      <c r="AU8" s="446" t="s">
         <v>206</v>
       </c>
-      <c r="AV8" s="444" t="s">
+      <c r="AV8" s="443" t="s">
         <v>207</v>
       </c>
-      <c r="AW8" s="470" t="s">
+      <c r="AW8" s="469" t="s">
         <v>208</v>
       </c>
-      <c r="AX8" s="444" t="s">
+      <c r="AX8" s="443" t="s">
         <v>24</v>
       </c>
-      <c r="AY8" s="510" t="s">
+      <c r="AY8" s="509" t="s">
         <v>235</v>
       </c>
-      <c r="AZ8" s="511"/>
-      <c r="BA8" s="511"/>
-      <c r="BB8" s="511"/>
-      <c r="BC8" s="511"/>
-      <c r="BD8" s="511"/>
-      <c r="BE8" s="511"/>
-      <c r="BF8" s="511"/>
-      <c r="BG8" s="511"/>
-      <c r="BH8" s="511"/>
-      <c r="BI8" s="511"/>
-      <c r="BJ8" s="511"/>
-      <c r="BK8" s="511"/>
-      <c r="BL8" s="511"/>
-      <c r="BM8" s="511"/>
-      <c r="BN8" s="511"/>
-      <c r="BO8" s="511"/>
-      <c r="BP8" s="512"/>
-      <c r="BQ8" s="503" t="s">
+      <c r="AZ8" s="510"/>
+      <c r="BA8" s="510"/>
+      <c r="BB8" s="510"/>
+      <c r="BC8" s="510"/>
+      <c r="BD8" s="510"/>
+      <c r="BE8" s="510"/>
+      <c r="BF8" s="510"/>
+      <c r="BG8" s="510"/>
+      <c r="BH8" s="510"/>
+      <c r="BI8" s="510"/>
+      <c r="BJ8" s="510"/>
+      <c r="BK8" s="510"/>
+      <c r="BL8" s="510"/>
+      <c r="BM8" s="510"/>
+      <c r="BN8" s="510"/>
+      <c r="BO8" s="510"/>
+      <c r="BP8" s="511"/>
+      <c r="BQ8" s="502" t="s">
         <v>220</v>
       </c>
-      <c r="BR8" s="504"/>
-      <c r="BS8" s="444" t="s">
+      <c r="BR8" s="503"/>
+      <c r="BS8" s="443" t="s">
         <v>221</v>
       </c>
-      <c r="BT8" s="444" t="s">
+      <c r="BT8" s="443" t="s">
         <v>222</v>
       </c>
       <c r="BU8" s="337" t="s">
         <v>223</v>
       </c>
-      <c r="BV8" s="492" t="s">
+      <c r="BV8" s="491" t="s">
         <v>232</v>
       </c>
-      <c r="BW8" s="493"/>
-      <c r="BX8" s="493"/>
-      <c r="BY8" s="494"/>
+      <c r="BW8" s="492"/>
+      <c r="BX8" s="492"/>
+      <c r="BY8" s="493"/>
       <c r="BZ8" s="419" t="s">
         <v>228</v>
       </c>
@@ -15989,208 +15993,208 @@
       <c r="CG8" s="331"/>
     </row>
     <row r="9" spans="1:85" s="330" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A9" s="449"/>
-      <c r="B9" s="450"/>
-      <c r="C9" s="451"/>
-      <c r="D9" s="452"/>
-      <c r="E9" s="452"/>
-      <c r="F9" s="453"/>
-      <c r="G9" s="454"/>
-      <c r="H9" s="455"/>
-      <c r="I9" s="455"/>
-      <c r="J9" s="454"/>
-      <c r="K9" s="466" t="s">
+      <c r="A9" s="448"/>
+      <c r="B9" s="449"/>
+      <c r="C9" s="450"/>
+      <c r="D9" s="451"/>
+      <c r="E9" s="451"/>
+      <c r="F9" s="452"/>
+      <c r="G9" s="453"/>
+      <c r="H9" s="454"/>
+      <c r="I9" s="454"/>
+      <c r="J9" s="453"/>
+      <c r="K9" s="465" t="s">
         <v>169</v>
       </c>
-      <c r="L9" s="466" t="s">
+      <c r="L9" s="465" t="s">
         <v>170</v>
       </c>
-      <c r="M9" s="466" t="s">
+      <c r="M9" s="465" t="s">
         <v>171</v>
       </c>
-      <c r="N9" s="466" t="s">
+      <c r="N9" s="465" t="s">
         <v>172</v>
       </c>
-      <c r="O9" s="466" t="s">
+      <c r="O9" s="465" t="s">
         <v>173</v>
       </c>
-      <c r="P9" s="466" t="s">
+      <c r="P9" s="465" t="s">
         <v>174</v>
       </c>
-      <c r="Q9" s="466" t="s">
+      <c r="Q9" s="465" t="s">
         <v>175</v>
       </c>
-      <c r="R9" s="466" t="s">
+      <c r="R9" s="465" t="s">
         <v>176</v>
       </c>
-      <c r="S9" s="466" t="s">
+      <c r="S9" s="465" t="s">
         <v>177</v>
       </c>
-      <c r="T9" s="466" t="s">
+      <c r="T9" s="465" t="s">
         <v>178</v>
       </c>
-      <c r="U9" s="466" t="s">
+      <c r="U9" s="465" t="s">
         <v>179</v>
       </c>
-      <c r="V9" s="462" t="s">
+      <c r="V9" s="461" t="s">
         <v>180</v>
       </c>
-      <c r="W9" s="463"/>
-      <c r="X9" s="466" t="s">
+      <c r="W9" s="462"/>
+      <c r="X9" s="465" t="s">
         <v>183</v>
       </c>
-      <c r="Y9" s="467" t="s">
+      <c r="Y9" s="466" t="s">
         <v>47</v>
       </c>
-      <c r="Z9" s="467" t="s">
+      <c r="Z9" s="466" t="s">
         <v>184</v>
       </c>
-      <c r="AA9" s="467" t="s">
+      <c r="AA9" s="466" t="s">
         <v>185</v>
       </c>
-      <c r="AB9" s="467" t="s">
+      <c r="AB9" s="466" t="s">
         <v>186</v>
       </c>
-      <c r="AC9" s="467" t="s">
+      <c r="AC9" s="466" t="s">
         <v>187</v>
       </c>
-      <c r="AD9" s="467" t="s">
+      <c r="AD9" s="466" t="s">
         <v>188</v>
       </c>
-      <c r="AE9" s="467" t="s">
+      <c r="AE9" s="466" t="s">
         <v>189</v>
       </c>
-      <c r="AF9" s="467" t="s">
+      <c r="AF9" s="466" t="s">
         <v>190</v>
       </c>
-      <c r="AG9" s="467" t="s">
+      <c r="AG9" s="466" t="s">
         <v>191</v>
       </c>
-      <c r="AH9" s="467" t="s">
+      <c r="AH9" s="466" t="s">
         <v>192</v>
       </c>
-      <c r="AI9" s="467" t="s">
+      <c r="AI9" s="466" t="s">
         <v>193</v>
       </c>
-      <c r="AJ9" s="468" t="s">
+      <c r="AJ9" s="467" t="s">
         <v>194</v>
       </c>
-      <c r="AK9" s="469" t="s">
+      <c r="AK9" s="468" t="s">
         <v>195</v>
       </c>
-      <c r="AL9" s="470" t="s">
+      <c r="AL9" s="469" t="s">
         <v>196</v>
       </c>
-      <c r="AM9" s="467" t="s">
+      <c r="AM9" s="466" t="s">
         <v>197</v>
       </c>
-      <c r="AN9" s="444" t="s">
+      <c r="AN9" s="443" t="s">
         <v>198</v>
       </c>
-      <c r="AO9" s="444" t="s">
+      <c r="AO9" s="443" t="s">
         <v>199</v>
       </c>
-      <c r="AP9" s="454"/>
-      <c r="AQ9" s="454"/>
-      <c r="AR9" s="454"/>
-      <c r="AS9" s="454"/>
-      <c r="AT9" s="454"/>
-      <c r="AU9" s="454"/>
-      <c r="AV9" s="451"/>
-      <c r="AW9" s="475"/>
-      <c r="AX9" s="451"/>
-      <c r="AY9" s="507" t="s">
+      <c r="AP9" s="453"/>
+      <c r="AQ9" s="453"/>
+      <c r="AR9" s="453"/>
+      <c r="AS9" s="453"/>
+      <c r="AT9" s="453"/>
+      <c r="AU9" s="453"/>
+      <c r="AV9" s="450"/>
+      <c r="AW9" s="474"/>
+      <c r="AX9" s="450"/>
+      <c r="AY9" s="506" t="s">
         <v>234</v>
       </c>
-      <c r="AZ9" s="508"/>
-      <c r="BA9" s="508"/>
-      <c r="BB9" s="508"/>
-      <c r="BC9" s="508"/>
-      <c r="BD9" s="508"/>
-      <c r="BE9" s="508"/>
-      <c r="BF9" s="508"/>
-      <c r="BG9" s="508"/>
-      <c r="BH9" s="508"/>
-      <c r="BI9" s="508"/>
-      <c r="BJ9" s="509"/>
-      <c r="BK9" s="507" t="s">
+      <c r="AZ9" s="507"/>
+      <c r="BA9" s="507"/>
+      <c r="BB9" s="507"/>
+      <c r="BC9" s="507"/>
+      <c r="BD9" s="507"/>
+      <c r="BE9" s="507"/>
+      <c r="BF9" s="507"/>
+      <c r="BG9" s="507"/>
+      <c r="BH9" s="507"/>
+      <c r="BI9" s="507"/>
+      <c r="BJ9" s="508"/>
+      <c r="BK9" s="506" t="s">
         <v>233</v>
       </c>
-      <c r="BL9" s="508"/>
-      <c r="BM9" s="508"/>
-      <c r="BN9" s="508"/>
-      <c r="BO9" s="508"/>
-      <c r="BP9" s="509"/>
-      <c r="BQ9" s="451" t="s">
+      <c r="BL9" s="507"/>
+      <c r="BM9" s="507"/>
+      <c r="BN9" s="507"/>
+      <c r="BO9" s="507"/>
+      <c r="BP9" s="508"/>
+      <c r="BQ9" s="450" t="s">
         <v>65</v>
       </c>
-      <c r="BR9" s="451" t="s">
+      <c r="BR9" s="450" t="s">
         <v>219</v>
       </c>
-      <c r="BS9" s="451"/>
-      <c r="BT9" s="451"/>
-      <c r="BU9" s="501"/>
-      <c r="BV9" s="495"/>
-      <c r="BW9" s="496"/>
-      <c r="BX9" s="496"/>
-      <c r="BY9" s="497"/>
-      <c r="BZ9" s="490"/>
-      <c r="CA9" s="490"/>
-      <c r="CB9" s="490"/>
+      <c r="BS9" s="450"/>
+      <c r="BT9" s="450"/>
+      <c r="BU9" s="500"/>
+      <c r="BV9" s="494"/>
+      <c r="BW9" s="495"/>
+      <c r="BX9" s="495"/>
+      <c r="BY9" s="496"/>
+      <c r="BZ9" s="489"/>
+      <c r="CA9" s="489"/>
+      <c r="CB9" s="489"/>
       <c r="CF9" s="331"/>
       <c r="CG9" s="331"/>
     </row>
     <row r="10" spans="1:85" s="332" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A10" s="449"/>
-      <c r="B10" s="450"/>
-      <c r="C10" s="451"/>
-      <c r="D10" s="452"/>
-      <c r="E10" s="452"/>
-      <c r="F10" s="453"/>
-      <c r="G10" s="454"/>
-      <c r="H10" s="455"/>
-      <c r="I10" s="455"/>
-      <c r="J10" s="454"/>
-      <c r="K10" s="471"/>
-      <c r="L10" s="471"/>
-      <c r="M10" s="471"/>
-      <c r="N10" s="471"/>
-      <c r="O10" s="471"/>
-      <c r="P10" s="471"/>
-      <c r="Q10" s="471"/>
-      <c r="R10" s="471"/>
-      <c r="S10" s="471"/>
-      <c r="T10" s="471"/>
-      <c r="U10" s="471"/>
-      <c r="V10" s="464"/>
-      <c r="W10" s="465"/>
-      <c r="X10" s="471"/>
-      <c r="Y10" s="472"/>
-      <c r="Z10" s="472"/>
-      <c r="AA10" s="472"/>
-      <c r="AB10" s="472"/>
-      <c r="AC10" s="472"/>
-      <c r="AD10" s="472"/>
-      <c r="AE10" s="472"/>
-      <c r="AF10" s="472"/>
-      <c r="AG10" s="472"/>
-      <c r="AH10" s="472"/>
-      <c r="AI10" s="472"/>
-      <c r="AJ10" s="473"/>
-      <c r="AK10" s="474"/>
-      <c r="AL10" s="475"/>
-      <c r="AM10" s="472"/>
-      <c r="AN10" s="451"/>
-      <c r="AO10" s="451"/>
-      <c r="AP10" s="454"/>
-      <c r="AQ10" s="454"/>
-      <c r="AR10" s="454"/>
-      <c r="AS10" s="454"/>
-      <c r="AT10" s="454"/>
-      <c r="AU10" s="454"/>
-      <c r="AV10" s="451"/>
-      <c r="AW10" s="475"/>
-      <c r="AX10" s="451"/>
+      <c r="A10" s="448"/>
+      <c r="B10" s="449"/>
+      <c r="C10" s="450"/>
+      <c r="D10" s="451"/>
+      <c r="E10" s="451"/>
+      <c r="F10" s="452"/>
+      <c r="G10" s="453"/>
+      <c r="H10" s="454"/>
+      <c r="I10" s="454"/>
+      <c r="J10" s="453"/>
+      <c r="K10" s="470"/>
+      <c r="L10" s="470"/>
+      <c r="M10" s="470"/>
+      <c r="N10" s="470"/>
+      <c r="O10" s="470"/>
+      <c r="P10" s="470"/>
+      <c r="Q10" s="470"/>
+      <c r="R10" s="470"/>
+      <c r="S10" s="470"/>
+      <c r="T10" s="470"/>
+      <c r="U10" s="470"/>
+      <c r="V10" s="463"/>
+      <c r="W10" s="464"/>
+      <c r="X10" s="470"/>
+      <c r="Y10" s="471"/>
+      <c r="Z10" s="471"/>
+      <c r="AA10" s="471"/>
+      <c r="AB10" s="471"/>
+      <c r="AC10" s="471"/>
+      <c r="AD10" s="471"/>
+      <c r="AE10" s="471"/>
+      <c r="AF10" s="471"/>
+      <c r="AG10" s="471"/>
+      <c r="AH10" s="471"/>
+      <c r="AI10" s="471"/>
+      <c r="AJ10" s="472"/>
+      <c r="AK10" s="473"/>
+      <c r="AL10" s="474"/>
+      <c r="AM10" s="471"/>
+      <c r="AN10" s="450"/>
+      <c r="AO10" s="450"/>
+      <c r="AP10" s="453"/>
+      <c r="AQ10" s="453"/>
+      <c r="AR10" s="453"/>
+      <c r="AS10" s="453"/>
+      <c r="AT10" s="453"/>
+      <c r="AU10" s="453"/>
+      <c r="AV10" s="450"/>
+      <c r="AW10" s="474"/>
+      <c r="AX10" s="450"/>
       <c r="AY10" s="329" t="s">
         <v>67</v>
       </c>
@@ -16200,63 +16204,63 @@
       <c r="BA10" s="329" t="s">
         <v>69</v>
       </c>
-      <c r="BB10" s="505" t="s">
+      <c r="BB10" s="504" t="s">
         <v>209</v>
       </c>
-      <c r="BC10" s="484" t="s">
+      <c r="BC10" s="483" t="s">
         <v>71</v>
       </c>
-      <c r="BD10" s="484" t="s">
+      <c r="BD10" s="483" t="s">
         <v>210</v>
       </c>
-      <c r="BE10" s="482" t="s">
+      <c r="BE10" s="481" t="s">
         <v>145</v>
       </c>
-      <c r="BF10" s="482" t="s">
+      <c r="BF10" s="481" t="s">
         <v>211</v>
       </c>
-      <c r="BG10" s="482" t="s">
+      <c r="BG10" s="481" t="s">
         <v>212</v>
       </c>
-      <c r="BH10" s="484" t="s">
+      <c r="BH10" s="483" t="s">
         <v>76</v>
       </c>
-      <c r="BI10" s="482" t="s">
+      <c r="BI10" s="481" t="s">
         <v>79</v>
       </c>
-      <c r="BJ10" s="488" t="s">
+      <c r="BJ10" s="487" t="s">
         <v>213</v>
       </c>
-      <c r="BK10" s="484" t="s">
+      <c r="BK10" s="483" t="s">
         <v>214</v>
       </c>
-      <c r="BL10" s="486" t="s">
+      <c r="BL10" s="485" t="s">
         <v>215</v>
       </c>
-      <c r="BM10" s="484" t="s">
+      <c r="BM10" s="483" t="s">
         <v>216</v>
       </c>
-      <c r="BN10" s="486" t="s">
+      <c r="BN10" s="485" t="s">
         <v>217</v>
       </c>
-      <c r="BO10" s="486" t="s">
+      <c r="BO10" s="485" t="s">
         <v>218</v>
       </c>
-      <c r="BP10" s="444" t="s">
+      <c r="BP10" s="443" t="s">
         <v>85</v>
       </c>
-      <c r="BQ10" s="451"/>
-      <c r="BR10" s="451"/>
-      <c r="BS10" s="451"/>
-      <c r="BT10" s="451"/>
-      <c r="BU10" s="502"/>
-      <c r="BV10" s="498"/>
-      <c r="BW10" s="499"/>
-      <c r="BX10" s="499"/>
-      <c r="BY10" s="500"/>
-      <c r="BZ10" s="491"/>
-      <c r="CA10" s="491"/>
-      <c r="CB10" s="491"/>
+      <c r="BQ10" s="450"/>
+      <c r="BR10" s="450"/>
+      <c r="BS10" s="450"/>
+      <c r="BT10" s="450"/>
+      <c r="BU10" s="501"/>
+      <c r="BV10" s="497"/>
+      <c r="BW10" s="498"/>
+      <c r="BX10" s="498"/>
+      <c r="BY10" s="499"/>
+      <c r="BZ10" s="490"/>
+      <c r="CA10" s="490"/>
+      <c r="CB10" s="490"/>
       <c r="CC10" s="228" t="s">
         <v>231</v>
       </c>
@@ -16264,59 +16268,59 @@
       <c r="CG10" s="331"/>
     </row>
     <row r="11" spans="1:85" s="332" customFormat="1" ht="38.25" customHeight="1">
-      <c r="A11" s="456"/>
-      <c r="B11" s="457"/>
+      <c r="A11" s="455"/>
+      <c r="B11" s="456"/>
       <c r="C11" s="437"/>
-      <c r="D11" s="458"/>
-      <c r="E11" s="458"/>
-      <c r="F11" s="459"/>
-      <c r="G11" s="460"/>
-      <c r="H11" s="461"/>
-      <c r="I11" s="461"/>
-      <c r="J11" s="460"/>
-      <c r="K11" s="476"/>
-      <c r="L11" s="476"/>
-      <c r="M11" s="476"/>
-      <c r="N11" s="476"/>
-      <c r="O11" s="476"/>
-      <c r="P11" s="476"/>
-      <c r="Q11" s="476"/>
-      <c r="R11" s="476"/>
-      <c r="S11" s="476"/>
-      <c r="T11" s="476"/>
-      <c r="U11" s="476"/>
-      <c r="V11" s="481" t="s">
+      <c r="D11" s="457"/>
+      <c r="E11" s="457"/>
+      <c r="F11" s="458"/>
+      <c r="G11" s="459"/>
+      <c r="H11" s="460"/>
+      <c r="I11" s="460"/>
+      <c r="J11" s="459"/>
+      <c r="K11" s="475"/>
+      <c r="L11" s="475"/>
+      <c r="M11" s="475"/>
+      <c r="N11" s="475"/>
+      <c r="O11" s="475"/>
+      <c r="P11" s="475"/>
+      <c r="Q11" s="475"/>
+      <c r="R11" s="475"/>
+      <c r="S11" s="475"/>
+      <c r="T11" s="475"/>
+      <c r="U11" s="475"/>
+      <c r="V11" s="480" t="s">
         <v>181</v>
       </c>
-      <c r="W11" s="481" t="s">
+      <c r="W11" s="480" t="s">
         <v>182</v>
       </c>
-      <c r="X11" s="476"/>
-      <c r="Y11" s="477"/>
-      <c r="Z11" s="477"/>
-      <c r="AA11" s="477"/>
-      <c r="AB11" s="477"/>
-      <c r="AC11" s="477"/>
-      <c r="AD11" s="477"/>
-      <c r="AE11" s="477"/>
-      <c r="AF11" s="477"/>
-      <c r="AG11" s="477"/>
-      <c r="AH11" s="477"/>
-      <c r="AI11" s="477"/>
-      <c r="AJ11" s="478"/>
-      <c r="AK11" s="479"/>
-      <c r="AL11" s="480"/>
-      <c r="AM11" s="477"/>
+      <c r="X11" s="475"/>
+      <c r="Y11" s="476"/>
+      <c r="Z11" s="476"/>
+      <c r="AA11" s="476"/>
+      <c r="AB11" s="476"/>
+      <c r="AC11" s="476"/>
+      <c r="AD11" s="476"/>
+      <c r="AE11" s="476"/>
+      <c r="AF11" s="476"/>
+      <c r="AG11" s="476"/>
+      <c r="AH11" s="476"/>
+      <c r="AI11" s="476"/>
+      <c r="AJ11" s="477"/>
+      <c r="AK11" s="478"/>
+      <c r="AL11" s="479"/>
+      <c r="AM11" s="476"/>
       <c r="AN11" s="437"/>
       <c r="AO11" s="437"/>
-      <c r="AP11" s="460"/>
-      <c r="AQ11" s="460"/>
-      <c r="AR11" s="460"/>
-      <c r="AS11" s="460"/>
-      <c r="AT11" s="460"/>
-      <c r="AU11" s="460"/>
+      <c r="AP11" s="459"/>
+      <c r="AQ11" s="459"/>
+      <c r="AR11" s="459"/>
+      <c r="AS11" s="459"/>
+      <c r="AT11" s="459"/>
+      <c r="AU11" s="459"/>
       <c r="AV11" s="437"/>
-      <c r="AW11" s="480"/>
+      <c r="AW11" s="479"/>
       <c r="AX11" s="437"/>
       <c r="AY11" s="229" t="s">
         <v>88</v>
@@ -16327,26 +16331,26 @@
       <c r="BA11" s="229" t="s">
         <v>90</v>
       </c>
-      <c r="BB11" s="506"/>
-      <c r="BC11" s="485"/>
-      <c r="BD11" s="485"/>
-      <c r="BE11" s="483"/>
-      <c r="BF11" s="483"/>
-      <c r="BG11" s="483"/>
-      <c r="BH11" s="485"/>
-      <c r="BI11" s="483"/>
-      <c r="BJ11" s="489"/>
-      <c r="BK11" s="485"/>
-      <c r="BL11" s="487"/>
-      <c r="BM11" s="485"/>
-      <c r="BN11" s="487"/>
-      <c r="BO11" s="487"/>
+      <c r="BB11" s="505"/>
+      <c r="BC11" s="484"/>
+      <c r="BD11" s="484"/>
+      <c r="BE11" s="482"/>
+      <c r="BF11" s="482"/>
+      <c r="BG11" s="482"/>
+      <c r="BH11" s="484"/>
+      <c r="BI11" s="482"/>
+      <c r="BJ11" s="488"/>
+      <c r="BK11" s="484"/>
+      <c r="BL11" s="486"/>
+      <c r="BM11" s="484"/>
+      <c r="BN11" s="486"/>
+      <c r="BO11" s="486"/>
       <c r="BP11" s="437"/>
       <c r="BQ11" s="437"/>
       <c r="BR11" s="437"/>
       <c r="BS11" s="437"/>
       <c r="BT11" s="437"/>
-      <c r="BU11" s="502"/>
+      <c r="BU11" s="501"/>
       <c r="BV11" s="237" t="s">
         <v>224</v>
       </c>
@@ -16359,9 +16363,9 @@
       <c r="BY11" s="238" t="s">
         <v>227</v>
       </c>
-      <c r="BZ11" s="491"/>
-      <c r="CA11" s="491"/>
-      <c r="CB11" s="491"/>
+      <c r="BZ11" s="490"/>
+      <c r="CA11" s="490"/>
+      <c r="CB11" s="490"/>
       <c r="CC11" s="227">
         <v>25</v>
       </c>
@@ -18700,7 +18704,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A12:CG21" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
-  <mergeCells count="81">
+  <mergeCells count="80">
     <mergeCell ref="H8:H11"/>
     <mergeCell ref="J8:J11"/>
     <mergeCell ref="AT8:AT11"/>
@@ -18739,7 +18743,6 @@
     <mergeCell ref="BT8:BT11"/>
     <mergeCell ref="E8:E11"/>
     <mergeCell ref="G8:G11"/>
-    <mergeCell ref="BU3:BZ6"/>
     <mergeCell ref="AU8:AU11"/>
     <mergeCell ref="BS8:BS11"/>
     <mergeCell ref="BK9:BP9"/>
@@ -19205,7 +19208,7 @@
       <c r="E5" s="411" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="441" t="s">
+      <c r="F5" s="440" t="s">
         <v>142</v>
       </c>
       <c r="G5" s="404" t="s">
